--- a/docs/saenggibu-form.xlsx
+++ b/docs/saenggibu-form.xlsx
@@ -815,7 +815,7 @@
     <row r="7" spans="1:28" ht="24" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="str">
         <f t="shared" ref="A7:A70" si="0">C7&amp;TEXT(D7,"00")&amp;TEXT(E7,"00")</f>
-        <v>21307</v>
+        <v>0000</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -833,7 +833,7 @@
     <row r="8" spans="1:28" ht="60" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>21312</v>
+        <v>0000</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -845,7 +845,7 @@
     <row r="9" spans="1:28" ht="84" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>21314</v>
+        <v>0000</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -857,7 +857,7 @@
     <row r="10" spans="1:28" ht="108" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>21318</v>
+        <v>0000</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -869,7 +869,7 @@
     <row r="11" spans="1:28" ht="96" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>21321</v>
+        <v>0000</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -881,7 +881,7 @@
     <row r="12" spans="1:28" ht="24" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>21403</v>
+        <v>0000</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
